--- a/Protocol/ApplicationProtocol.xlsx
+++ b/Protocol/ApplicationProtocol.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Santase\Protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E862E73-64E2-4557-8FD2-B97385CFFBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82356DC6-A20F-4789-A7A4-2B000415407B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="102">
   <si>
     <t>Client -&gt; Server</t>
   </si>
@@ -45,72 +45,21 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Join()</t>
-  </si>
-  <si>
-    <t>/PlayerInfo (int playerID)</t>
-  </si>
-  <si>
-    <t>Private reply to requester. Assigns playerId = 0 : 1</t>
-  </si>
-  <si>
-    <t>PlayCard()</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>cardIndex</t>
   </si>
   <si>
-    <t>/CardPlayed (int playerID, string name, string suit)</t>
-  </si>
-  <si>
-    <t>/Notification (string msg) on invalid move</t>
-  </si>
-  <si>
-    <t>Only allowed on player's turn</t>
-  </si>
-  <si>
-    <t>If invalid, server rejects and state does not change</t>
-  </si>
-  <si>
-    <t>CloseDeck()</t>
-  </si>
-  <si>
     <t>playerID</t>
   </si>
   <si>
-    <t>/DeckClosed (int playerID)</t>
-  </si>
-  <si>
-    <t>Only allowed after trick 0</t>
-  </si>
-  <si>
-    <t>/Notification (string msg) on invalid attempt</t>
-  </si>
-  <si>
-    <t>If invalid, nothing changes</t>
-  </si>
-  <si>
-    <t>ExchangeKoz()</t>
-  </si>
-  <si>
-    <t>/KozChanged (string name, string suit)</t>
-  </si>
-  <si>
-    <t>Only allowed in Phase 1. Only if player has 9 of trump</t>
-  </si>
-  <si>
     <t>Server -&gt; Client</t>
   </si>
   <si>
     <t>PlayerInfo</t>
   </si>
   <si>
-    <t>Private</t>
-  </si>
-  <si>
     <t>Sent once on join</t>
   </si>
   <si>
@@ -132,9 +81,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Trump card name</t>
-  </si>
-  <si>
     <t>suit</t>
   </si>
   <si>
@@ -162,9 +108,6 @@
     <t>CardPlayed</t>
   </si>
   <si>
-    <t>Who played the card</t>
-  </si>
-  <si>
     <t>Card name</t>
   </si>
   <si>
@@ -186,15 +129,9 @@
     <t>p1GamePoints</t>
   </si>
   <si>
-    <t>Game points for Player 1</t>
-  </si>
-  <si>
     <t>p2GamePoints</t>
   </si>
   <si>
-    <t>Game points for Player 2</t>
-  </si>
-  <si>
     <t>DeckClosed</t>
   </si>
   <si>
@@ -207,25 +144,193 @@
     <t>message</t>
   </si>
   <si>
-    <t>Text message from server</t>
-  </si>
-  <si>
     <t>StateChanged</t>
   </si>
   <si>
-    <t>Phase changed (Phase1 / Phase2 / Closed)</t>
-  </si>
-  <si>
     <t>MatchOver</t>
   </si>
   <si>
     <t>Match winner</t>
   </si>
   <si>
-    <t xml:space="preserve">int </t>
-  </si>
-  <si>
     <t>OSC Network Protocol</t>
+  </si>
+  <si>
+    <t>JoinRoom</t>
+  </si>
+  <si>
+    <t>roomName</t>
+  </si>
+  <si>
+    <t>RoomJoinSuccess(roomID, playerID)</t>
+  </si>
+  <si>
+    <t>Join existing room</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>RoomJoinFailed(reason)</t>
+  </si>
+  <si>
+    <t>CreateRoom</t>
+  </si>
+  <si>
+    <t>RoomCreated(roomID)</t>
+  </si>
+  <si>
+    <t>Create new room</t>
+  </si>
+  <si>
+    <t>RoomCreatedFailed(reason)</t>
+  </si>
+  <si>
+    <t>Disconnect</t>
+  </si>
+  <si>
+    <t>Client disconnects</t>
+  </si>
+  <si>
+    <t>HelloClient</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Sent once on connect</t>
+  </si>
+  <si>
+    <t>Ping</t>
+  </si>
+  <si>
+    <t>Heartbeat</t>
+  </si>
+  <si>
+    <t>PlayCard</t>
+  </si>
+  <si>
+    <t>CardPlayed(playerID, name, suit, points)</t>
+  </si>
+  <si>
+    <t>Only on player's turn</t>
+  </si>
+  <si>
+    <t>Notification(msg)</t>
+  </si>
+  <si>
+    <t>On invalid move</t>
+  </si>
+  <si>
+    <t>CloseDeck</t>
+  </si>
+  <si>
+    <t>DeckClosed(playerID)</t>
+  </si>
+  <si>
+    <t>Only after trick 0 and before last 2 cards</t>
+  </si>
+  <si>
+    <t>On invalid attempt</t>
+  </si>
+  <si>
+    <t>ExchangeKoz</t>
+  </si>
+  <si>
+    <t>KozChanged(name, suit)</t>
+  </si>
+  <si>
+    <t>Only in Phase 1</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>RoomInfo</t>
+  </si>
+  <si>
+    <t>roomID</t>
+  </si>
+  <si>
+    <t>RoomCreated</t>
+  </si>
+  <si>
+    <t>Room created</t>
+  </si>
+  <si>
+    <t>RoomCreatedFailed</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>Creation failed</t>
+  </si>
+  <si>
+    <t>RoomJoinSuccess</t>
+  </si>
+  <si>
+    <t>Joined room</t>
+  </si>
+  <si>
+    <t>RoomJoinFailed</t>
+  </si>
+  <si>
+    <t>Join failed</t>
+  </si>
+  <si>
+    <t>PlayerDisconnected</t>
+  </si>
+  <si>
+    <t>Opponent disconnected</t>
+  </si>
+  <si>
+    <t>Whose hand changed</t>
+  </si>
+  <si>
+    <t>cardCount</t>
+  </si>
+  <si>
+    <t>Number of cards</t>
+  </si>
+  <si>
+    <t>string,int,int</t>
+  </si>
+  <si>
+    <t>name,suit,points</t>
+  </si>
+  <si>
+    <t>Owner only</t>
+  </si>
+  <si>
+    <t>Opponent receives empty cards</t>
+  </si>
+  <si>
+    <t>Trump name</t>
+  </si>
+  <si>
+    <t>Who played</t>
+  </si>
+  <si>
+    <t>points</t>
+  </si>
+  <si>
+    <t>Card points</t>
+  </si>
+  <si>
+    <t>Trick finished</t>
+  </si>
+  <si>
+    <t>Game points P1</t>
+  </si>
+  <si>
+    <t>Game points P2</t>
+  </si>
+  <si>
+    <t>Text message</t>
+  </si>
+  <si>
+    <t>Phase changed</t>
   </si>
 </sst>
 </file>
@@ -335,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -350,28 +455,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -653,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="22.08984375" bestFit="1" customWidth="1"/>
@@ -664,13 +767,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.5" x14ac:dyDescent="0.65">
-      <c r="B1" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1"/>
@@ -695,442 +798,677 @@
     </row>
     <row r="5" spans="1:6" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="3"/>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
-      <c r="B7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>8</v>
+      <c r="B7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B13" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B14" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B24" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B25" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="12" t="s">
+      <c r="C25" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B26" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B27" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B31" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B32" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B36" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B9" s="11"/>
-      <c r="C9" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="12" t="s">
+      <c r="C36" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B10" s="10" t="s">
+      <c r="D36" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="E36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="E37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9" t="s">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B38" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="C38" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B12" s="12" t="s">
+      <c r="E38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="12" t="s">
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B39" s="8"/>
+      <c r="C39" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="E39" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B40" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="7" t="s">
+      <c r="C40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B24" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="8" t="s">
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B41" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B45" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B26" s="12" t="s">
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B46" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="10" t="s">
+      <c r="C46" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="E46" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="10" t="s">
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B47" s="8"/>
+      <c r="C47" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E47" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="E48" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B49" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B29" s="10"/>
-      <c r="C29" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="C49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="10" t="s">
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B50" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="12" t="s">
+      <c r="C50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="11" t="s">
+      <c r="E50" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B51" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="11" t="s">
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B52" s="8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B31" s="12"/>
-      <c r="C31" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="11" t="s">
+      <c r="C52" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B32" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B34" s="12"/>
-      <c r="C34" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B35" s="12"/>
-      <c r="C35" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="10"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B38" s="12"/>
-      <c r="C38" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="12"/>
-      <c r="C39" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B40" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B41" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B42" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B43" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
